--- a/results/04_final_refined_daily_hydroclimate_data/702/Daily_all_temperatures.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/702/Daily_all_temperatures.xlsx
@@ -485,15 +485,9 @@
       <c r="C2" t="n">
         <v>1</v>
       </c>
-      <c r="D2" t="n">
-        <v>27.9</v>
-      </c>
-      <c r="E2" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="F2" t="n">
-        <v>18.5</v>
-      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
@@ -508,15 +502,9 @@
       <c r="C3" t="n">
         <v>2</v>
       </c>
-      <c r="D3" t="n">
-        <v>26.9</v>
-      </c>
-      <c r="E3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="F3" t="n">
-        <v>19.2</v>
-      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
@@ -531,15 +519,9 @@
       <c r="C4" t="n">
         <v>3</v>
       </c>
-      <c r="D4" t="n">
-        <v>25.9</v>
-      </c>
-      <c r="E4" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="F4" t="n">
-        <v>18.4</v>
-      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
@@ -554,15 +536,9 @@
       <c r="C5" t="n">
         <v>4</v>
       </c>
-      <c r="D5" t="n">
-        <v>21.9</v>
-      </c>
-      <c r="E5" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="F5" t="n">
-        <v>17.4</v>
-      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
@@ -577,15 +553,9 @@
       <c r="C6" t="n">
         <v>5</v>
       </c>
-      <c r="D6" t="n">
-        <v>26.3</v>
-      </c>
-      <c r="E6" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="F6" t="n">
-        <v>18.4</v>
-      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
@@ -620,14 +590,10 @@
         <v>7</v>
       </c>
       <c r="D8" t="n">
-        <v>25.9</v>
-      </c>
-      <c r="E8" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="F8" t="n">
-        <v>18.4</v>
-      </c>
+        <v>25.11</v>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
@@ -643,7 +609,7 @@
         <v>8</v>
       </c>
       <c r="D9" t="n">
-        <v>25.35</v>
+        <v>25.3</v>
       </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
@@ -662,14 +628,10 @@
         <v>9</v>
       </c>
       <c r="D10" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="E10" t="n">
-        <v>13</v>
-      </c>
-      <c r="F10" t="n">
-        <v>18.2</v>
-      </c>
+        <v>23.5</v>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
@@ -687,12 +649,8 @@
       <c r="D11" t="n">
         <v>26</v>
       </c>
-      <c r="E11" t="n">
-        <v>11</v>
-      </c>
-      <c r="F11" t="n">
-        <v>18.5</v>
-      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
@@ -707,7 +665,9 @@
       <c r="C12" t="n">
         <v>11</v>
       </c>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" t="n">
+        <v>25.9</v>
+      </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
@@ -724,7 +684,9 @@
       <c r="C13" t="n">
         <v>12</v>
       </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="D13" t="n">
+        <v>28</v>
+      </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
@@ -741,7 +703,9 @@
       <c r="C14" t="n">
         <v>13</v>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="n">
+        <v>28.2</v>
+      </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
@@ -758,7 +722,9 @@
       <c r="C15" t="n">
         <v>14</v>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="n">
+        <v>24.8</v>
+      </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
@@ -775,7 +741,9 @@
       <c r="C16" t="n">
         <v>15</v>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="n">
+        <v>25.2</v>
+      </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
@@ -794,7 +762,9 @@
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
+      <c r="F17" t="n">
+        <v>7.8</v>
+      </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
@@ -811,7 +781,9 @@
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
+      <c r="F18" t="n">
+        <v>17</v>
+      </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
@@ -828,7 +800,9 @@
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
+      <c r="F19" t="n">
+        <v>18.1</v>
+      </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
@@ -845,7 +819,9 @@
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
+      <c r="F20" t="n">
+        <v>49.3</v>
+      </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
@@ -862,7 +838,9 @@
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
+      <c r="F21" t="n">
+        <v>4.5</v>
+      </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
@@ -877,15 +855,9 @@
       <c r="C22" t="n">
         <v>21</v>
       </c>
-      <c r="D22" t="n">
-        <v>26.3</v>
-      </c>
-      <c r="E22" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="F22" t="n">
-        <v>18.4</v>
-      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
@@ -917,15 +889,9 @@
       <c r="C24" t="n">
         <v>23</v>
       </c>
-      <c r="D24" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="E24" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="F24" t="n">
-        <v>18.5</v>
-      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
@@ -1008,15 +974,9 @@
       <c r="C29" t="n">
         <v>28</v>
       </c>
-      <c r="D29" t="n">
-        <v>27.2</v>
-      </c>
-      <c r="E29" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="F29" t="n">
-        <v>18.9</v>
-      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
@@ -1048,15 +1008,9 @@
       <c r="C31" t="n">
         <v>1</v>
       </c>
-      <c r="D31" t="n">
-        <v>25.9</v>
-      </c>
-      <c r="E31" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="F31" t="n">
-        <v>19.9</v>
-      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
@@ -1071,15 +1025,9 @@
       <c r="C32" t="n">
         <v>2</v>
       </c>
-      <c r="D32" t="n">
-        <v>26.6</v>
-      </c>
-      <c r="E32" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="F32" t="n">
-        <v>20.3</v>
-      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
@@ -1094,15 +1042,9 @@
       <c r="C33" t="n">
         <v>3</v>
       </c>
-      <c r="D33" t="n">
-        <v>24.3</v>
-      </c>
-      <c r="E33" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="F33" t="n">
-        <v>19.4</v>
-      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
@@ -1117,15 +1059,9 @@
       <c r="C34" t="n">
         <v>4</v>
       </c>
-      <c r="D34" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="E34" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="F34" t="n">
-        <v>19.9</v>
-      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
@@ -1140,15 +1076,9 @@
       <c r="C35" t="n">
         <v>5</v>
       </c>
-      <c r="D35" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="E35" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="F35" t="n">
-        <v>19.6</v>
-      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
@@ -1249,9 +1179,7 @@
         <v>11</v>
       </c>
       <c r="D41" t="inlineStr"/>
-      <c r="E41" t="n">
-        <v>14.3</v>
-      </c>
+      <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr"/>
@@ -1267,15 +1195,9 @@
       <c r="C42" t="n">
         <v>12</v>
       </c>
-      <c r="D42" t="n">
-        <v>26.8</v>
-      </c>
-      <c r="E42" t="n">
-        <v>13</v>
-      </c>
-      <c r="F42" t="n">
-        <v>19.9</v>
-      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr"/>
@@ -1290,15 +1212,9 @@
       <c r="C43" t="n">
         <v>13</v>
       </c>
-      <c r="D43" t="n">
-        <v>25.3</v>
-      </c>
-      <c r="E43" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="F43" t="n">
-        <v>19.1</v>
-      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr"/>
@@ -1313,15 +1229,9 @@
       <c r="C44" t="n">
         <v>14</v>
       </c>
-      <c r="D44" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="E44" t="n">
-        <v>14</v>
-      </c>
-      <c r="F44" t="n">
-        <v>19.8</v>
-      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr"/>
@@ -1336,15 +1246,9 @@
       <c r="C45" t="n">
         <v>15</v>
       </c>
-      <c r="D45" t="n">
-        <v>25.4</v>
-      </c>
-      <c r="E45" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="F45" t="n">
-        <v>19.3</v>
-      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr"/>
@@ -1410,15 +1314,9 @@
       <c r="C49" t="n">
         <v>19</v>
       </c>
-      <c r="D49" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="E49" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="F49" t="n">
-        <v>18.5</v>
-      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr"/>
@@ -1535,15 +1433,9 @@
       <c r="C56" t="n">
         <v>26</v>
       </c>
-      <c r="D56" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="E56" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="F56" t="n">
-        <v>18.4</v>
-      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr"/>
@@ -1558,15 +1450,9 @@
       <c r="C57" t="n">
         <v>27</v>
       </c>
-      <c r="D57" t="n">
-        <v>25.9</v>
-      </c>
-      <c r="E57" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="F57" t="n">
-        <v>18.5</v>
-      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr"/>
@@ -1581,15 +1467,9 @@
       <c r="C58" t="n">
         <v>28</v>
       </c>
-      <c r="D58" t="n">
-        <v>26</v>
-      </c>
-      <c r="E58" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="F58" t="n">
-        <v>17.9</v>
-      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr"/>

--- a/results/04_final_refined_daily_hydroclimate_data/702/Daily_all_temperatures.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/702/Daily_all_temperatures.xlsx
@@ -485,9 +485,15 @@
       <c r="C2" t="n">
         <v>1</v>
       </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
+      <c r="D2" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="E2" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="F2" t="n">
+        <v>18.5</v>
+      </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
@@ -502,7 +508,9 @@
       <c r="C3" t="n">
         <v>2</v>
       </c>
-      <c r="D3" t="inlineStr"/>
+      <c r="D3" t="n">
+        <v>26.9</v>
+      </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
@@ -519,9 +527,15 @@
       <c r="C4" t="n">
         <v>3</v>
       </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
+      <c r="D4" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="E4" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="F4" t="n">
+        <v>18.4</v>
+      </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
@@ -536,7 +550,9 @@
       <c r="C5" t="n">
         <v>4</v>
       </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="n">
+        <v>21.9</v>
+      </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
@@ -553,7 +569,9 @@
       <c r="C6" t="n">
         <v>5</v>
       </c>
-      <c r="D6" t="inlineStr"/>
+      <c r="D6" t="n">
+        <v>26.1</v>
+      </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
@@ -573,8 +591,12 @@
       <c r="D7" t="n">
         <v>27.3</v>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
+      <c r="E7" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="F7" t="n">
+        <v>19</v>
+      </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
@@ -590,10 +612,14 @@
         <v>7</v>
       </c>
       <c r="D8" t="n">
-        <v>25.11</v>
-      </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
+        <v>25.9</v>
+      </c>
+      <c r="E8" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="F8" t="n">
+        <v>18.4</v>
+      </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
@@ -608,9 +634,7 @@
       <c r="C9" t="n">
         <v>8</v>
       </c>
-      <c r="D9" t="n">
-        <v>25.3</v>
-      </c>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
@@ -628,10 +652,14 @@
         <v>9</v>
       </c>
       <c r="D10" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
+        <v>23.8</v>
+      </c>
+      <c r="E10" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="F10" t="n">
+        <v>18.13</v>
+      </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
@@ -668,8 +696,12 @@
       <c r="D12" t="n">
         <v>25.9</v>
       </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
+      <c r="E12" t="n">
+        <v>24.44</v>
+      </c>
+      <c r="F12" t="n">
+        <v>25.2</v>
+      </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
@@ -687,8 +719,12 @@
       <c r="D13" t="n">
         <v>28</v>
       </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
+      <c r="E13" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="F13" t="n">
+        <v>19.3</v>
+      </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
@@ -726,7 +762,9 @@
         <v>24.8</v>
       </c>
       <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
+      <c r="F15" t="n">
+        <v>12.6</v>
+      </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
@@ -762,9 +800,7 @@
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
-      <c r="F17" t="n">
-        <v>7.8</v>
-      </c>
+      <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
@@ -781,9 +817,7 @@
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
-      <c r="F18" t="n">
-        <v>17</v>
-      </c>
+      <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
@@ -800,9 +834,7 @@
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
-      <c r="F19" t="n">
-        <v>18.1</v>
-      </c>
+      <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
@@ -819,9 +851,7 @@
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
-      <c r="F20" t="n">
-        <v>49.3</v>
-      </c>
+      <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
@@ -838,9 +868,7 @@
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
-      <c r="F21" t="n">
-        <v>4.5</v>
-      </c>
+      <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
@@ -855,9 +883,15 @@
       <c r="C22" t="n">
         <v>21</v>
       </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
+      <c r="D22" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="E22" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="F22" t="n">
+        <v>19.5</v>
+      </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
@@ -957,9 +991,15 @@
       <c r="C28" t="n">
         <v>27</v>
       </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
+      <c r="D28" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="E28" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="F28" t="n">
+        <v>18.9</v>
+      </c>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
@@ -1008,9 +1048,15 @@
       <c r="C31" t="n">
         <v>1</v>
       </c>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
+      <c r="D31" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="E31" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="F31" t="n">
+        <v>19.9</v>
+      </c>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
@@ -1025,9 +1071,15 @@
       <c r="C32" t="n">
         <v>2</v>
       </c>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
+      <c r="D32" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="E32" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="F32" t="n">
+        <v>20.5</v>
+      </c>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
@@ -1042,9 +1094,15 @@
       <c r="C33" t="n">
         <v>3</v>
       </c>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
+      <c r="D33" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="E33" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="F33" t="n">
+        <v>19.3</v>
+      </c>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
@@ -1059,9 +1117,15 @@
       <c r="C34" t="n">
         <v>4</v>
       </c>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
+      <c r="D34" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="E34" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="F34" t="n">
+        <v>19.9</v>
+      </c>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
@@ -1076,9 +1140,15 @@
       <c r="C35" t="n">
         <v>5</v>
       </c>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
+      <c r="D35" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="E35" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="F35" t="n">
+        <v>19.6</v>
+      </c>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
@@ -1178,9 +1248,15 @@
       <c r="C41" t="n">
         <v>11</v>
       </c>
-      <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr"/>
+      <c r="D41" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="E41" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="F41" t="n">
+        <v>19.1</v>
+      </c>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
@@ -1195,9 +1271,15 @@
       <c r="C42" t="n">
         <v>12</v>
       </c>
-      <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr"/>
+      <c r="D42" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="E42" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="F42" t="n">
+        <v>19.3</v>
+      </c>
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr"/>
@@ -1247,7 +1329,9 @@
         <v>15</v>
       </c>
       <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr"/>
+      <c r="E45" t="n">
+        <v>13.2</v>
+      </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr"/>
@@ -1280,9 +1364,15 @@
       <c r="C47" t="n">
         <v>17</v>
       </c>
-      <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr"/>
+      <c r="D47" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="E47" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="F47" t="n">
+        <v>18.9</v>
+      </c>
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr"/>
@@ -1314,9 +1404,15 @@
       <c r="C49" t="n">
         <v>19</v>
       </c>
-      <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr"/>
+      <c r="D49" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="E49" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="F49" t="n">
+        <v>18.8</v>
+      </c>
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr"/>
@@ -1365,9 +1461,15 @@
       <c r="C52" t="n">
         <v>22</v>
       </c>
-      <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr"/>
+      <c r="D52" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="E52" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="F52" t="n">
+        <v>18.4</v>
+      </c>
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr"/>
@@ -1382,9 +1484,15 @@
       <c r="C53" t="n">
         <v>23</v>
       </c>
-      <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr"/>
+      <c r="D53" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="E53" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="F53" t="n">
+        <v>17.4</v>
+      </c>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr"/>
@@ -1399,9 +1507,15 @@
       <c r="C54" t="n">
         <v>24</v>
       </c>
-      <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr"/>
+      <c r="D54" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="E54" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="F54" t="n">
+        <v>18.1</v>
+      </c>
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr"/>
@@ -1433,9 +1547,15 @@
       <c r="C56" t="n">
         <v>26</v>
       </c>
-      <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr"/>
-      <c r="F56" t="inlineStr"/>
+      <c r="D56" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="E56" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="F56" t="n">
+        <v>18.9</v>
+      </c>
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr"/>
@@ -1450,9 +1570,15 @@
       <c r="C57" t="n">
         <v>27</v>
       </c>
-      <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr"/>
-      <c r="F57" t="inlineStr"/>
+      <c r="D57" t="n">
+        <v>26</v>
+      </c>
+      <c r="E57" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="F57" t="n">
+        <v>17.9</v>
+      </c>
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr"/>
@@ -1467,9 +1593,15 @@
       <c r="C58" t="n">
         <v>28</v>
       </c>
-      <c r="D58" t="inlineStr"/>
-      <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr"/>
+      <c r="D58" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="E58" t="n">
+        <v>10</v>
+      </c>
+      <c r="F58" t="n">
+        <v>18.1</v>
+      </c>
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr"/>
@@ -1484,7 +1616,9 @@
       <c r="C59" t="n">
         <v>29</v>
       </c>
-      <c r="D59" t="inlineStr"/>
+      <c r="D59" t="n">
+        <v>26.9</v>
+      </c>
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr"/>
@@ -1501,9 +1635,13 @@
       <c r="C60" t="n">
         <v>30</v>
       </c>
-      <c r="D60" t="inlineStr"/>
+      <c r="D60" t="n">
+        <v>26.1</v>
+      </c>
       <c r="E60" t="inlineStr"/>
-      <c r="F60" t="inlineStr"/>
+      <c r="F60" t="n">
+        <v>19.2</v>
+      </c>
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr"/>

--- a/results/04_final_refined_daily_hydroclimate_data/702/Daily_all_temperatures.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/702/Daily_all_temperatures.xlsx
@@ -511,8 +511,12 @@
       <c r="D3" t="n">
         <v>26.9</v>
       </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
+      <c r="E3" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="F3" t="n">
+        <v>19.2</v>
+      </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
@@ -551,10 +555,14 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>21.9</v>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
+        <v>21.6</v>
+      </c>
+      <c r="E5" t="n">
+        <v>13</v>
+      </c>
+      <c r="F5" t="n">
+        <v>17.3</v>
+      </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
@@ -570,10 +578,14 @@
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>26.1</v>
-      </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
+        <v>26.8</v>
+      </c>
+      <c r="E6" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="F6" t="n">
+        <v>18.6</v>
+      </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
@@ -611,15 +623,9 @@
       <c r="C8" t="n">
         <v>7</v>
       </c>
-      <c r="D8" t="n">
-        <v>25.9</v>
-      </c>
-      <c r="E8" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="F8" t="n">
-        <v>18.4</v>
-      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
@@ -634,9 +640,15 @@
       <c r="C9" t="n">
         <v>8</v>
       </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
+      <c r="D9" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="E9" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="F9" t="n">
+        <v>18.2</v>
+      </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
@@ -651,15 +663,9 @@
       <c r="C10" t="n">
         <v>9</v>
       </c>
-      <c r="D10" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="E10" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="F10" t="n">
-        <v>18.13</v>
-      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
@@ -677,8 +683,12 @@
       <c r="D11" t="n">
         <v>26</v>
       </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
+      <c r="E11" t="n">
+        <v>11</v>
+      </c>
+      <c r="F11" t="n">
+        <v>18.5</v>
+      </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
@@ -696,12 +706,8 @@
       <c r="D12" t="n">
         <v>25.9</v>
       </c>
-      <c r="E12" t="n">
-        <v>24.44</v>
-      </c>
-      <c r="F12" t="n">
-        <v>25.2</v>
-      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
@@ -761,9 +767,11 @@
       <c r="D15" t="n">
         <v>24.8</v>
       </c>
-      <c r="E15" t="inlineStr"/>
+      <c r="E15" t="n">
+        <v>12.6</v>
+      </c>
       <c r="F15" t="n">
-        <v>12.6</v>
+        <v>18.7</v>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
@@ -782,8 +790,12 @@
       <c r="D16" t="n">
         <v>25.2</v>
       </c>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
+      <c r="E16" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="F16" t="n">
+        <v>18.6</v>
+      </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
@@ -798,9 +810,15 @@
       <c r="C17" t="n">
         <v>16</v>
       </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
+      <c r="D17" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="E17" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="F17" t="n">
+        <v>17.8</v>
+      </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
@@ -815,9 +833,15 @@
       <c r="C18" t="n">
         <v>17</v>
       </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
+      <c r="D18" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="E18" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="F18" t="n">
+        <v>17</v>
+      </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
@@ -832,9 +856,15 @@
       <c r="C19" t="n">
         <v>18</v>
       </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
+      <c r="D19" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="E19" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="F19" t="n">
+        <v>18.1</v>
+      </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
@@ -849,9 +879,15 @@
       <c r="C20" t="n">
         <v>19</v>
       </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
+      <c r="D20" t="n">
+        <v>23</v>
+      </c>
+      <c r="E20" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="F20" t="n">
+        <v>19.3</v>
+      </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
@@ -866,9 +902,15 @@
       <c r="C21" t="n">
         <v>20</v>
       </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
+      <c r="D21" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="E21" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="F21" t="n">
+        <v>19.5</v>
+      </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
@@ -884,10 +926,10 @@
         <v>21</v>
       </c>
       <c r="D22" t="n">
-        <v>27.2</v>
+        <v>28.1</v>
       </c>
       <c r="E22" t="n">
-        <v>10.3</v>
+        <v>10.9</v>
       </c>
       <c r="F22" t="n">
         <v>19.5</v>
@@ -906,9 +948,15 @@
       <c r="C23" t="n">
         <v>22</v>
       </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
+      <c r="D23" t="n">
+        <v>25</v>
+      </c>
+      <c r="E23" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="F23" t="n">
+        <v>18.9</v>
+      </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
@@ -923,9 +971,15 @@
       <c r="C24" t="n">
         <v>23</v>
       </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
+      <c r="D24" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="E24" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="F24" t="n">
+        <v>19.1</v>
+      </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
@@ -940,9 +994,15 @@
       <c r="C25" t="n">
         <v>24</v>
       </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
+      <c r="D25" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="E25" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="F25" t="n">
+        <v>19.8</v>
+      </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
@@ -957,9 +1017,15 @@
       <c r="C26" t="n">
         <v>25</v>
       </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
+      <c r="D26" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="E26" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="F26" t="n">
+        <v>18.4</v>
+      </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
@@ -974,9 +1040,15 @@
       <c r="C27" t="n">
         <v>26</v>
       </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
+      <c r="D27" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="E27" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="F27" t="n">
+        <v>18.9</v>
+      </c>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
@@ -992,10 +1064,10 @@
         <v>27</v>
       </c>
       <c r="D28" t="n">
-        <v>27.1</v>
+        <v>27.6</v>
       </c>
       <c r="E28" t="n">
-        <v>10.6</v>
+        <v>10.2</v>
       </c>
       <c r="F28" t="n">
         <v>18.9</v>
@@ -1031,9 +1103,15 @@
       <c r="C30" t="n">
         <v>29</v>
       </c>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
+      <c r="D30" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="E30" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="F30" t="n">
+        <v>19.3</v>
+      </c>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
@@ -1072,10 +1150,10 @@
         <v>2</v>
       </c>
       <c r="D32" t="n">
-        <v>25.5</v>
+        <v>27</v>
       </c>
       <c r="E32" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="F32" t="n">
         <v>20.5</v>
@@ -1095,13 +1173,13 @@
         <v>3</v>
       </c>
       <c r="D33" t="n">
-        <v>24.9</v>
+        <v>23.2</v>
       </c>
       <c r="E33" t="n">
-        <v>13.7</v>
+        <v>15.1</v>
       </c>
       <c r="F33" t="n">
-        <v>19.3</v>
+        <v>19.7</v>
       </c>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr"/>
@@ -1118,10 +1196,10 @@
         <v>4</v>
       </c>
       <c r="D34" t="n">
-        <v>25.3</v>
+        <v>25.2</v>
       </c>
       <c r="E34" t="n">
-        <v>14.6</v>
+        <v>14.5</v>
       </c>
       <c r="F34" t="n">
         <v>19.9</v>
@@ -1141,10 +1219,10 @@
         <v>5</v>
       </c>
       <c r="D35" t="n">
-        <v>24.4</v>
+        <v>25.2</v>
       </c>
       <c r="E35" t="n">
-        <v>14.8</v>
+        <v>14</v>
       </c>
       <c r="F35" t="n">
         <v>19.6</v>
@@ -1214,9 +1292,15 @@
       <c r="C39" t="n">
         <v>9</v>
       </c>
-      <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
+      <c r="D39" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="E39" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="F39" t="n">
+        <v>19.6</v>
+      </c>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr"/>
@@ -1231,9 +1315,15 @@
       <c r="C40" t="n">
         <v>10</v>
       </c>
-      <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
+      <c r="D40" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="E40" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="F40" t="n">
+        <v>20.8</v>
+      </c>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
@@ -1272,13 +1362,13 @@
         <v>12</v>
       </c>
       <c r="D42" t="n">
-        <v>22.4</v>
+        <v>25.7</v>
       </c>
       <c r="E42" t="n">
-        <v>16.2</v>
+        <v>14.2</v>
       </c>
       <c r="F42" t="n">
-        <v>19.3</v>
+        <v>19.93</v>
       </c>
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr"/>
@@ -1294,9 +1384,15 @@
       <c r="C43" t="n">
         <v>13</v>
       </c>
-      <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr"/>
+      <c r="D43" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="E43" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="F43" t="n">
+        <v>19.58</v>
+      </c>
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr"/>
@@ -1311,9 +1407,15 @@
       <c r="C44" t="n">
         <v>14</v>
       </c>
-      <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr"/>
+      <c r="D44" t="n">
+        <v>26</v>
+      </c>
+      <c r="E44" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="F44" t="n">
+        <v>19.8</v>
+      </c>
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr"/>
@@ -1328,11 +1430,15 @@
       <c r="C45" t="n">
         <v>15</v>
       </c>
-      <c r="D45" t="inlineStr"/>
+      <c r="D45" t="n">
+        <v>25.3</v>
+      </c>
       <c r="E45" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="F45" t="inlineStr"/>
+        <v>13.5</v>
+      </c>
+      <c r="F45" t="n">
+        <v>19.4</v>
+      </c>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr"/>
@@ -1347,9 +1453,15 @@
       <c r="C46" t="n">
         <v>16</v>
       </c>
-      <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr"/>
+      <c r="D46" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="E46" t="n">
+        <v>15.39</v>
+      </c>
+      <c r="F46" t="n">
+        <v>19.3</v>
+      </c>
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr"/>
@@ -1365,10 +1477,10 @@
         <v>17</v>
       </c>
       <c r="D47" t="n">
-        <v>22.4</v>
+        <v>22.5</v>
       </c>
       <c r="E47" t="n">
-        <v>15.3</v>
+        <v>15.4</v>
       </c>
       <c r="F47" t="n">
         <v>18.9</v>
@@ -1387,9 +1499,15 @@
       <c r="C48" t="n">
         <v>18</v>
       </c>
-      <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr"/>
-      <c r="F48" t="inlineStr"/>
+      <c r="D48" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="E48" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="F48" t="n">
+        <v>18.9</v>
+      </c>
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr"/>
@@ -1427,9 +1545,15 @@
       <c r="C50" t="n">
         <v>20</v>
       </c>
-      <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr"/>
+      <c r="D50" t="n">
+        <v>23</v>
+      </c>
+      <c r="E50" t="n">
+        <v>14</v>
+      </c>
+      <c r="F50" t="n">
+        <v>18.6</v>
+      </c>
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr"/>
@@ -1462,13 +1586,13 @@
         <v>22</v>
       </c>
       <c r="D52" t="n">
-        <v>23.1</v>
+        <v>23.7</v>
       </c>
       <c r="E52" t="n">
-        <v>13.7</v>
+        <v>13.9</v>
       </c>
       <c r="F52" t="n">
-        <v>18.4</v>
+        <v>18.8</v>
       </c>
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr"/>
@@ -1485,13 +1609,13 @@
         <v>23</v>
       </c>
       <c r="D53" t="n">
-        <v>19.7</v>
+        <v>20.5</v>
       </c>
       <c r="E53" t="n">
         <v>15.1</v>
       </c>
       <c r="F53" t="n">
-        <v>17.4</v>
+        <v>17.8</v>
       </c>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr"/>
@@ -1508,13 +1632,13 @@
         <v>24</v>
       </c>
       <c r="D54" t="n">
-        <v>24.1</v>
+        <v>24.3</v>
       </c>
       <c r="E54" t="n">
         <v>12.1</v>
       </c>
       <c r="F54" t="n">
-        <v>18.1</v>
+        <v>18.18</v>
       </c>
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr"/>
@@ -1548,10 +1672,10 @@
         <v>26</v>
       </c>
       <c r="D56" t="n">
-        <v>25.9</v>
+        <v>25.1</v>
       </c>
       <c r="E56" t="n">
-        <v>11.9</v>
+        <v>11.1</v>
       </c>
       <c r="F56" t="n">
         <v>18.9</v>
@@ -1571,10 +1695,10 @@
         <v>27</v>
       </c>
       <c r="D57" t="n">
-        <v>26</v>
+        <v>26.1</v>
       </c>
       <c r="E57" t="n">
-        <v>9.800000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="F57" t="n">
         <v>17.9</v>
@@ -1619,8 +1743,12 @@
       <c r="D59" t="n">
         <v>26.9</v>
       </c>
-      <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr"/>
+      <c r="E59" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="F59" t="n">
+        <v>18.6</v>
+      </c>
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr"/>

--- a/results/04_final_refined_daily_hydroclimate_data/702/Daily_all_temperatures.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/702/Daily_all_temperatures.xlsx
@@ -555,13 +555,13 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>21.6</v>
+        <v>21.9</v>
       </c>
       <c r="E5" t="n">
-        <v>13</v>
+        <v>12.9</v>
       </c>
       <c r="F5" t="n">
-        <v>17.3</v>
+        <v>17.4</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
@@ -578,13 +578,13 @@
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>26.8</v>
+        <v>27.3</v>
       </c>
       <c r="E6" t="n">
-        <v>10.4</v>
+        <v>10.5</v>
       </c>
       <c r="F6" t="n">
-        <v>18.6</v>
+        <v>18.9</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
@@ -600,15 +600,9 @@
       <c r="C7" t="n">
         <v>6</v>
       </c>
-      <c r="D7" t="n">
-        <v>27.3</v>
-      </c>
-      <c r="E7" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="F7" t="n">
-        <v>19</v>
-      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
@@ -641,7 +635,7 @@
         <v>8</v>
       </c>
       <c r="D9" t="n">
-        <v>25.5</v>
+        <v>25.4</v>
       </c>
       <c r="E9" t="n">
         <v>11.3</v>
@@ -706,8 +700,12 @@
       <c r="D12" t="n">
         <v>25.9</v>
       </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
+      <c r="E12" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="F12" t="n">
+        <v>18.4</v>
+      </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
@@ -748,8 +746,12 @@
       <c r="D14" t="n">
         <v>28.2</v>
       </c>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
+      <c r="E14" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="F14" t="n">
+        <v>19.3</v>
+      </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
@@ -765,13 +767,13 @@
         <v>14</v>
       </c>
       <c r="D15" t="n">
-        <v>24.8</v>
+        <v>24.5</v>
       </c>
       <c r="E15" t="n">
         <v>12.6</v>
       </c>
       <c r="F15" t="n">
-        <v>18.7</v>
+        <v>18.9</v>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
@@ -791,10 +793,10 @@
         <v>25.2</v>
       </c>
       <c r="E16" t="n">
-        <v>12.1</v>
+        <v>12.2</v>
       </c>
       <c r="F16" t="n">
-        <v>18.6</v>
+        <v>18.7</v>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
@@ -811,11 +813,9 @@
         <v>16</v>
       </c>
       <c r="D17" t="n">
-        <v>25.9</v>
-      </c>
-      <c r="E17" t="n">
-        <v>9.699999999999999</v>
-      </c>
+        <v>32.7</v>
+      </c>
+      <c r="E17" t="inlineStr"/>
       <c r="F17" t="n">
         <v>17.8</v>
       </c>
@@ -857,10 +857,10 @@
         <v>18</v>
       </c>
       <c r="D19" t="n">
-        <v>24.5</v>
+        <v>19.1</v>
       </c>
       <c r="E19" t="n">
-        <v>11.7</v>
+        <v>17.1</v>
       </c>
       <c r="F19" t="n">
         <v>18.1</v>
@@ -880,10 +880,10 @@
         <v>19</v>
       </c>
       <c r="D20" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E20" t="n">
-        <v>15.6</v>
+        <v>11.6</v>
       </c>
       <c r="F20" t="n">
         <v>19.3</v>
@@ -926,13 +926,13 @@
         <v>21</v>
       </c>
       <c r="D22" t="n">
-        <v>28.1</v>
+        <v>27.9</v>
       </c>
       <c r="E22" t="n">
-        <v>10.9</v>
+        <v>10.2</v>
       </c>
       <c r="F22" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
@@ -949,13 +949,13 @@
         <v>22</v>
       </c>
       <c r="D23" t="n">
-        <v>25</v>
+        <v>24.2</v>
       </c>
       <c r="E23" t="n">
         <v>12.8</v>
       </c>
       <c r="F23" t="n">
-        <v>18.9</v>
+        <v>18.5</v>
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
@@ -972,13 +972,13 @@
         <v>23</v>
       </c>
       <c r="D24" t="n">
-        <v>23.1</v>
+        <v>23.3</v>
       </c>
       <c r="E24" t="n">
         <v>14.7</v>
       </c>
       <c r="F24" t="n">
-        <v>19.1</v>
+        <v>19</v>
       </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
@@ -1018,13 +1018,13 @@
         <v>25</v>
       </c>
       <c r="D26" t="n">
-        <v>26.5</v>
+        <v>26.3</v>
       </c>
       <c r="E26" t="n">
-        <v>10.7</v>
+        <v>10.54</v>
       </c>
       <c r="F26" t="n">
-        <v>18.4</v>
+        <v>18.2</v>
       </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
@@ -1041,7 +1041,7 @@
         <v>26</v>
       </c>
       <c r="D27" t="n">
-        <v>26.9</v>
+        <v>26.8</v>
       </c>
       <c r="E27" t="n">
         <v>10.9</v>
@@ -1064,10 +1064,10 @@
         <v>27</v>
       </c>
       <c r="D28" t="n">
-        <v>27.6</v>
+        <v>27.1</v>
       </c>
       <c r="E28" t="n">
-        <v>10.2</v>
+        <v>10.7</v>
       </c>
       <c r="F28" t="n">
         <v>18.9</v>
@@ -1086,9 +1086,15 @@
       <c r="C29" t="n">
         <v>28</v>
       </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
+      <c r="D29" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="E29" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="F29" t="n">
+        <v>18.5</v>
+      </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
@@ -1130,7 +1136,7 @@
         <v>25.9</v>
       </c>
       <c r="E31" t="n">
-        <v>13.9</v>
+        <v>13.8</v>
       </c>
       <c r="F31" t="n">
         <v>19.9</v>
@@ -1150,13 +1156,13 @@
         <v>2</v>
       </c>
       <c r="D32" t="n">
-        <v>27</v>
+        <v>25.5</v>
       </c>
       <c r="E32" t="n">
-        <v>14</v>
+        <v>15.1</v>
       </c>
       <c r="F32" t="n">
-        <v>20.5</v>
+        <v>20.3</v>
       </c>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
@@ -1173,10 +1179,10 @@
         <v>3</v>
       </c>
       <c r="D33" t="n">
-        <v>23.2</v>
+        <v>24.9</v>
       </c>
       <c r="E33" t="n">
-        <v>15.1</v>
+        <v>14.5</v>
       </c>
       <c r="F33" t="n">
         <v>19.7</v>
@@ -1196,10 +1202,10 @@
         <v>4</v>
       </c>
       <c r="D34" t="n">
-        <v>25.2</v>
+        <v>25.3</v>
       </c>
       <c r="E34" t="n">
-        <v>14.5</v>
+        <v>14.6</v>
       </c>
       <c r="F34" t="n">
         <v>19.9</v>
@@ -1219,10 +1225,10 @@
         <v>5</v>
       </c>
       <c r="D35" t="n">
-        <v>25.2</v>
+        <v>24.4</v>
       </c>
       <c r="E35" t="n">
-        <v>14</v>
+        <v>14.8</v>
       </c>
       <c r="F35" t="n">
         <v>19.6</v>
@@ -1258,9 +1264,15 @@
       <c r="C37" t="n">
         <v>7</v>
       </c>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
+      <c r="D37" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="E37" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="F37" t="n">
+        <v>19.8</v>
+      </c>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
@@ -1361,15 +1373,9 @@
       <c r="C42" t="n">
         <v>12</v>
       </c>
-      <c r="D42" t="n">
-        <v>25.7</v>
-      </c>
-      <c r="E42" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="F42" t="n">
-        <v>19.93</v>
-      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr"/>
@@ -1384,15 +1390,9 @@
       <c r="C43" t="n">
         <v>13</v>
       </c>
-      <c r="D43" t="n">
-        <v>27.1</v>
-      </c>
-      <c r="E43" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="F43" t="n">
-        <v>19.58</v>
-      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr"/>
@@ -1408,10 +1408,10 @@
         <v>14</v>
       </c>
       <c r="D44" t="n">
-        <v>26</v>
+        <v>25.5</v>
       </c>
       <c r="E44" t="n">
-        <v>12.9</v>
+        <v>14.1</v>
       </c>
       <c r="F44" t="n">
         <v>19.8</v>
@@ -1430,15 +1430,9 @@
       <c r="C45" t="n">
         <v>15</v>
       </c>
-      <c r="D45" t="n">
-        <v>25.3</v>
-      </c>
-      <c r="E45" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="F45" t="n">
-        <v>19.4</v>
-      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr"/>
@@ -1453,15 +1447,9 @@
       <c r="C46" t="n">
         <v>16</v>
       </c>
-      <c r="D46" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="E46" t="n">
-        <v>15.39</v>
-      </c>
-      <c r="F46" t="n">
-        <v>19.3</v>
-      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr"/>
@@ -1545,15 +1533,9 @@
       <c r="C50" t="n">
         <v>20</v>
       </c>
-      <c r="D50" t="n">
-        <v>23</v>
-      </c>
-      <c r="E50" t="n">
-        <v>14</v>
-      </c>
-      <c r="F50" t="n">
-        <v>18.6</v>
-      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr"/>
@@ -1589,10 +1571,10 @@
         <v>23.7</v>
       </c>
       <c r="E52" t="n">
-        <v>13.9</v>
+        <v>13.7</v>
       </c>
       <c r="F52" t="n">
-        <v>18.8</v>
+        <v>18.7</v>
       </c>
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr"/>
@@ -1608,15 +1590,9 @@
       <c r="C53" t="n">
         <v>23</v>
       </c>
-      <c r="D53" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="E53" t="n">
-        <v>15.1</v>
-      </c>
-      <c r="F53" t="n">
-        <v>17.8</v>
-      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr"/>
@@ -1632,13 +1608,13 @@
         <v>24</v>
       </c>
       <c r="D54" t="n">
-        <v>24.3</v>
+        <v>24.1</v>
       </c>
       <c r="E54" t="n">
-        <v>12.1</v>
+        <v>12</v>
       </c>
       <c r="F54" t="n">
-        <v>18.18</v>
+        <v>18.1</v>
       </c>
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr"/>
@@ -1654,9 +1630,15 @@
       <c r="C55" t="n">
         <v>25</v>
       </c>
-      <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr"/>
+      <c r="D55" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="E55" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="F55" t="n">
+        <v>19.5</v>
+      </c>
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr"/>
@@ -1672,13 +1654,13 @@
         <v>26</v>
       </c>
       <c r="D56" t="n">
-        <v>25.1</v>
+        <v>25.9</v>
       </c>
       <c r="E56" t="n">
         <v>11.1</v>
       </c>
       <c r="F56" t="n">
-        <v>18.9</v>
+        <v>18.5</v>
       </c>
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr"/>
@@ -1721,10 +1703,10 @@
         <v>26.2</v>
       </c>
       <c r="E58" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="F58" t="n">
-        <v>18.1</v>
+        <v>22.1</v>
       </c>
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr"/>
